--- a/main/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/main/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:10:07+00:00</t>
+    <t>2026-09-22T15:44:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -469,7 +469,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J83-AutoriteEnregistrement-RASS/FHIR/JDV-J83-AutoriteEnregistrement-RASS|20240628120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J83-AutoriteEnregistrement-RASS/FHIR/JDV-J83-AutoriteEnregistrement-RASS|20260730120000</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1085,7 +1085,7 @@
     <t>Selecting a Service Category then determines the list of relevant service types that can be selected in the primary service type.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J132-ModaliteActivite-RASS/FHIR/JDV-J132-ModaliteActivite-RASS|20220325120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J132-ModaliteActivite-RASS/FHIR/JDV-J132-ModaliteActivite-RASS|20260730120000</t>
   </si>
   <si>
     <t>.code</t>
@@ -1125,7 +1125,7 @@
     <t>La discipline déterminant la nature de l’activité (CODE_ACT_SOIN).</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J133-ActiviteSanitaireRegulee-RASS/FHIR/JDV-J133-ActiviteSanitaireRegulee-RASS|20201127120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J133-ActiviteSanitaireRegulee-RASS/FHIR/JDV-J133-ActiviteSanitaireRegulee-RASS|20260827120000</t>
   </si>
   <si>
     <t>HealthcareService.specialty</t>
